--- a/Hoadon/HDVao/7/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/7/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TBN</t>
+          <t>C25TBR</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0315016765</t>
+          <t>0316158113</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ THÉP BÌNH NGUYÊN</t>
+          <t>CÔNG TY TNHH KHÍ HÓA LỎNG VIỆT NAM - VT GAS</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>66P Đường 6, Khu phố 3, Phường Phước Long , Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Phòng 606, tầng 6, Tòa nhà Waseco, số 10 Phổ Quang, Phường Tân Sơn Hòa, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1.8614274E7</v>
+        <v>4429511.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1489142.0</v>
+        <v>354361.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>2.0103416E7</v>
+        <v>4783872.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,56 +408,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TLP</t>
+          <t>C25TBR</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0316066744</t>
+          <t>0316158113</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG DỊCH VỤ LÂM PHƯƠNG</t>
+          <t>CÔNG TY TNHH KHÍ HÓA LỎNG VIỆT NAM - VT GAS</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>18E3 Chu Văn An, Phường Bình Thạnh, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Phòng 606, tầng 6, Tòa nhà Waseco, số 10 Phổ Quang, Phường Tân Sơn Hòa, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>4.1856E8</v>
+        <v>4429511.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>3.34848E7</v>
+        <v>354361.0</v>
       </c>
       <c r="M8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>4.520448E8</v>
+        <v>4783872.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -491,56 +491,54 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25TNH</t>
+          <t>C25TAH</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>15/07/2025</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3501030949</t>
+          <t>3500548590</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ NGỌC HẠNH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN A HÒ</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>204 Huyền Trân Công Chúa, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 109 - 111 Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>1328270.0</v>
+        <v>8981481.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>132827.0</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>718519.0</v>
+      </c>
+      <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>1461097.0</v>
+        <v>9700000.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -569,61 +567,55 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25TNH</t>
+          <t>C25TCV</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>92</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3501030949</t>
+          <t>3500830452</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ NGỌC HẠNH</t>
+          <t>HỘ KINH DOANH CƠ SỞ KINH DOANH CÁ VOI XANH</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>204 Huyền Trân Công Chúa, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>160/4 đường Hoàng Hoa Thám, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
-        </is>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>4536510.0</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>453651.0</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>0.0</v>
-      </c>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>4990161.0</v>
+        <v>1988000.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -657,56 +649,56 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25TBT</t>
+          <t>C25TMD</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3501772161</t>
+          <t>3501261826</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN BÊ TÔNG VÀ XÂY LẮP HODECO</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH ĐÔNG</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Thôn 9 Gò Găng, Xã Long Sơn, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 280/3 Trương Công Định, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1.63628889E8</v>
+        <v>2422560.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1.3090311E7</v>
+        <v>193805.0</v>
       </c>
       <c r="M11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>1.767192E8</v>
+        <v>2616365.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -724,6 +716,994 @@
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25TMD</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>8123</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3501261826</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH ĐÔNG</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Số 280/3 Trương Công Định, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>1877760.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>150221.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>2027981.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25THL</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>23750</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3501970854</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>3400000.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>272000.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>3672000.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25TVG</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3502411496</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM QUỐC TẾ VIETGROUP FOODS</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>128/1 đường Nguyễn Tất Thành, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>453704.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>36296.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>490000.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25TVG</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>10/07/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3502411496</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM QUỐC TẾ VIETGROUP FOODS</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>128/1 đường Nguyễn Tất Thành, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>458333.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>36667.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>495000.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>14/07/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường 11, Thành phố Vũng Tàu, Tỉnh Bà Rịa - Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>4333333.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>216667.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>4550000.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>19/07/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường 11, Thành phố Vũng Tàu, Tỉnh Bà Rịa - Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>4200000.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>210000.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>4410000.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>22/07/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>4425000.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>221250.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>4646250.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>4550000.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>227500.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>4777500.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25TCH</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>11/07/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3502470942</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>1.247705E7</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>623853.0</v>
+      </c>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>1.3100903E7</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25TCH</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3502470942</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>9524100.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>476205.0</v>
+      </c>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>1.0000305E7</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25TCH</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3502470942</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>4655000.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>232750.0</v>
+      </c>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>4887750.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25TLN</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>21/07/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3602750365</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CỒN - LÊ NGUYỄN</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>A2/189 B, KP 2, Phường Biên Hòa, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>4254640.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>340371.0</v>
+      </c>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>4595011.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>
